--- a/data/trans_camb/P38A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 1,34</t>
+          <t>-8,07; 0,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,84</t>
+          <t>-6,99; 1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 6,0</t>
+          <t>-2,13; 6,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,03</t>
+          <t>-4,95; 3,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,06</t>
+          <t>-4,47; 1,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,09</t>
+          <t>-5,11; 0,94</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,49</t>
+          <t>-8,71; 0,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,03</t>
+          <t>-7,55; 1,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 6,78</t>
+          <t>-2,29; 6,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,41</t>
+          <t>-5,26; 3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,3</t>
+          <t>-4,8; 1,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 1,18</t>
+          <t>-5,5; 1,04</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 2,04</t>
+          <t>-7,28; 2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,34</t>
+          <t>-5,63; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,26</t>
+          <t>-7,7; 0,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; -0,02</t>
+          <t>-8,76; -0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,06</t>
+          <t>-6,11; 0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,31</t>
+          <t>-6,12; 0,26</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,25</t>
+          <t>-8,01; 2,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,82</t>
+          <t>-6,09; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,27</t>
+          <t>-8,03; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -0,03</t>
+          <t>-9,19; -0,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,09</t>
+          <t>-6,54; 0,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,32</t>
+          <t>-6,55; 0,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,31</t>
+          <t>-5,54; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 0,92</t>
+          <t>-68,53; 1,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 6,59</t>
+          <t>-4,77; 5,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,63</t>
+          <t>-2,66; 6,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,85</t>
+          <t>-4,13; 2,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 1,43</t>
+          <t>-59,36; 1,54</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,62</t>
+          <t>-6,09; 2,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,35; 1,08</t>
+          <t>-74,79; 1,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,58</t>
+          <t>-5,09; 6,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 7,52</t>
+          <t>-2,8; 7,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,08</t>
+          <t>-4,59; 2,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 1,63</t>
+          <t>-65,85; 1,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,93</t>
+          <t>-4,03; 1,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,87</t>
+          <t>-6,23; 1,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,43</t>
+          <t>-2,6; 3,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,61</t>
+          <t>0,75; 8,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,87</t>
+          <t>-2,62; 1,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,38</t>
+          <t>-1,98; 4,38</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,22</t>
+          <t>-4,49; 2,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,99</t>
+          <t>-6,99; 1,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,93</t>
+          <t>-2,89; 4,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,0</t>
+          <t>0,84; 10,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,14</t>
+          <t>-2,93; 1,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,99</t>
+          <t>-2,21; 5,07</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 3,64</t>
+          <t>-5,06; 4,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 6,15</t>
+          <t>-4,17; 6,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,01</t>
+          <t>-5,45; 0,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-31,64; -0,25</t>
+          <t>-30,49; -0,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,24</t>
+          <t>-4,92; 0,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 0,57</t>
+          <t>-19,18; 0,7</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,48</t>
+          <t>-5,91; 5,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 7,53</t>
+          <t>-4,8; 7,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,01</t>
+          <t>-5,8; 0,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,0; -0,22</t>
+          <t>-32,99; -0,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,28</t>
+          <t>-5,46; 0,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 0,64</t>
+          <t>-21,12; 0,78</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 12,24</t>
+          <t>-5,34; 11,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 5,67</t>
+          <t>-18,08; 6,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,41</t>
+          <t>-0,37; 5,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,73</t>
+          <t>-5,35; 2,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,3</t>
+          <t>-0,87; 5,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -0,09</t>
+          <t>-9,04; -0,33</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 26,73</t>
+          <t>-10,27; 24,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 12,05</t>
+          <t>-33,57; 13,72</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 6,45</t>
+          <t>-0,41; 6,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,05</t>
+          <t>-6,15; 2,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 6,87</t>
+          <t>-1,09; 6,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -0,1</t>
+          <t>-11,29; -0,44</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,13</t>
+          <t>-3,43; 0,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-26,32; -0,92</t>
+          <t>-22,55; -1,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,56</t>
+          <t>-1,32; 1,59</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,26</t>
+          <t>-7,99; 1,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,44</t>
+          <t>-2,0; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -0,57</t>
+          <t>-15,24; -0,6</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,15</t>
+          <t>-3,98; 0,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -1,06</t>
+          <t>-26,23; -1,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,74</t>
+          <t>-1,47; 1,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,41</t>
+          <t>-8,87; 1,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,51</t>
+          <t>-2,26; 0,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -0,66</t>
+          <t>-17,37; -0,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-1,94</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 0,54</t>
+          <t>-7,95; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 1,59</t>
+          <t>-7,0; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,15</t>
+          <t>-1,86; 5,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,4</t>
+          <t>-5,53; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,75</t>
+          <t>-4,28; 1,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,94</t>
+          <t>-4,76; 0,93</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-2,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>-1,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,07%</t>
+          <t>-2,12%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 0,62</t>
+          <t>-8,54; 0,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,79</t>
+          <t>-7,68; 1,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,91</t>
+          <t>-1,98; 6,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,82</t>
+          <t>-5,85; 3,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,91</t>
+          <t>-4,61; 1,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,04</t>
+          <t>-5,13; 1,03</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,85</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 2,05</t>
+          <t>-7,31; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,17</t>
+          <t>-5,07; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,28</t>
+          <t>-7,92; 0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -0,64</t>
+          <t>-8,6; -0,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,05</t>
+          <t>-5,78; 0,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,26</t>
+          <t>-5,74; 0,19</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,87%</t>
+          <t>-4,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,93%</t>
+          <t>-3,09%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 2,28</t>
+          <t>-7,9; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,6</t>
+          <t>-5,56; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,28</t>
+          <t>-8,34; 0,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -0,7</t>
+          <t>-8,97; -0,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,05</t>
+          <t>-6,23; 0,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 0,25</t>
+          <t>-6,15; 0,18</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-32,9</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-26,0</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,82</t>
+          <t>-5,29; 2,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 1,5</t>
+          <t>-5,21; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,75</t>
+          <t>-4,48; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 6,78</t>
+          <t>-3,16; 6,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,25</t>
+          <t>-3,92; 2,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 1,54</t>
+          <t>-3,53; 3,1</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-36,63%</t>
+          <t>-1,17%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-28,82%</t>
+          <t>-0,23%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,05</t>
+          <t>-5,77; 2,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 1,72</t>
+          <t>-5,7; 3,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,53</t>
+          <t>-4,82; 7,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,75</t>
+          <t>-3,31; 7,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,5</t>
+          <t>-4,32; 2,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 1,61</t>
+          <t>-3,85; 3,48</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>-0,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,72</t>
+          <t>-3,8; 1,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,23</t>
+          <t>-5,47; 0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,82</t>
+          <t>-2,97; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,61</t>
+          <t>-0,86; 5,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,62</t>
+          <t>-2,47; 1,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,38</t>
+          <t>-2,87; 1,94</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-2,83%</t>
+          <t>-3,04%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>-0,68%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,0</t>
+          <t>-4,22; 2,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 1,43</t>
+          <t>-6,17; 0,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,4</t>
+          <t>-3,28; 3,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 10,01</t>
+          <t>-0,95; 5,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,86</t>
+          <t>-2,76; 2,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,07</t>
+          <t>-3,21; 2,24</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-8,79</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-3,21</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 4,1</t>
+          <t>-5,19; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,07</t>
+          <t>-9,23; 1,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,32</t>
+          <t>-5,61; 0,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-30,49; -0,35</t>
+          <t>-5,38; -0,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,39</t>
+          <t>-5,1; 0,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 0,7</t>
+          <t>-5,98; -0,58</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>-4,68%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-2,86%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,41%</t>
+          <t>-3,61%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 5,0</t>
+          <t>-6,11; 4,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,31</t>
+          <t>-10,74; 1,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,36</t>
+          <t>-5,95; 0,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,99; -0,38</t>
+          <t>-5,77; -0,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,43</t>
+          <t>-5,7; 0,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 0,78</t>
+          <t>-6,63; -0,64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-8,49</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-3,69</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-5,66</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 11,28</t>
+          <t>-5,74; 11,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 6,63</t>
+          <t>-19,92; 3,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,39</t>
+          <t>-0,15; 5,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,1</t>
+          <t>-7,12; 0,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,04</t>
+          <t>-1,06; 5,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -0,33</t>
+          <t>-10,05; -1,78</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-12,66%</t>
+          <t>-16,82%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-2,0%</t>
+          <t>-4,29%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-5,68%</t>
+          <t>-7,15%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 24,5</t>
+          <t>-10,6; 25,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 13,72</t>
+          <t>-37,26; 6,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,41</t>
+          <t>-0,16; 6,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,49</t>
+          <t>-8,28; 0,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,45</t>
+          <t>-1,3; 6,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,44</t>
+          <t>-12,63; -2,32</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-1,81</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,04</t>
+          <t>-3,48; 0,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,55; -1,13</t>
+          <t>-4,89; -0,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,59</t>
+          <t>-1,46; 1,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,17</t>
+          <t>-2,57; 0,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,26</t>
+          <t>-1,96; 0,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -0,6</t>
+          <t>-3,05; -0,5</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-9,03%</t>
+          <t>-3,02%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1,55%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-2,06%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,05</t>
+          <t>-4,05; 0,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,23; -1,33</t>
+          <t>-5,62; -0,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,78</t>
+          <t>-1,62; 1,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,3</t>
+          <t>-2,86; 0,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,3</t>
+          <t>-2,22; 0,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -0,69</t>
+          <t>-3,46; -0,58</t>
         </is>
       </c>
     </row>
